--- a/grupos/2AEV - Estadisticos 20232.xlsx
+++ b/grupos/2AEV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -197,24 +197,24 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Sanchez Hernández Raymundo</t>
+  </si>
+  <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Sanchez Hernández Raymundo</t>
-  </si>
-  <si>
     <t>Flores Paz Victor</t>
   </si>
   <si>
@@ -230,73 +230,97 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
     <t>BUSTOS</t>
   </si>
   <si>
+    <t>CERONIO</t>
+  </si>
+  <si>
     <t>LARA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
     <t>TEQUIHUATLE</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
+    <t>COCOTLE</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>JOSE EMILIANO</t>
   </si>
   <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
+    <t>ROBBIE ALONSO</t>
+  </si>
+  <si>
+    <t>ANTHONY</t>
+  </si>
+  <si>
+    <t>ALFONSO</t>
+  </si>
+  <si>
     <t>ISAAC</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
   </si>
 </sst>
 </file>
@@ -861,31 +885,31 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -927,7 +951,7 @@
         <v>7</v>
       </c>
       <c r="AG4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH4">
         <v>9</v>
@@ -936,7 +960,7 @@
         <v>6</v>
       </c>
       <c r="AJ4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AK4">
         <v>-1</v>
@@ -974,31 +998,31 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -1031,25 +1055,25 @@
         <v>6</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF5">
+        <v>8</v>
+      </c>
+      <c r="AG5">
         <v>9</v>
       </c>
-      <c r="AG5">
-        <v>8</v>
-      </c>
       <c r="AH5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI5">
         <v>9</v>
       </c>
       <c r="AJ5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK5">
         <v>-1</v>
@@ -1087,31 +1111,31 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -1141,28 +1165,28 @@
         <v>-1</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE6">
+        <v>10</v>
+      </c>
+      <c r="AF6">
+        <v>10</v>
+      </c>
+      <c r="AG6">
         <v>9</v>
       </c>
-      <c r="AF6">
+      <c r="AH6">
+        <v>10</v>
+      </c>
+      <c r="AI6">
+        <v>8</v>
+      </c>
+      <c r="AJ6">
         <v>9</v>
-      </c>
-      <c r="AG6">
-        <v>8</v>
-      </c>
-      <c r="AH6">
-        <v>10</v>
-      </c>
-      <c r="AI6">
-        <v>8</v>
-      </c>
-      <c r="AJ6">
-        <v>8</v>
       </c>
       <c r="AK6">
         <v>-1</v>
@@ -1200,31 +1224,31 @@
         <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1260,10 +1284,10 @@
         <v>5</v>
       </c>
       <c r="AE7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG7">
         <v>5</v>
@@ -1272,10 +1296,10 @@
         <v>6</v>
       </c>
       <c r="AI7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK7">
         <v>-1</v>
@@ -1313,31 +1337,31 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1426,31 +1450,31 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1483,25 +1507,25 @@
         <v>6</v>
       </c>
       <c r="AD9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE9">
         <v>6</v>
       </c>
       <c r="AF9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG9">
         <v>5</v>
       </c>
       <c r="AH9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK9">
         <v>-1</v>
@@ -1539,31 +1563,31 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1596,7 +1620,7 @@
         <v>6</v>
       </c>
       <c r="AD10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE10">
         <v>9</v>
@@ -1608,13 +1632,13 @@
         <v>8</v>
       </c>
       <c r="AH10">
+        <v>10</v>
+      </c>
+      <c r="AI10">
+        <v>8</v>
+      </c>
+      <c r="AJ10">
         <v>9</v>
-      </c>
-      <c r="AI10">
-        <v>8</v>
-      </c>
-      <c r="AJ10">
-        <v>8</v>
       </c>
       <c r="AK10">
         <v>-1</v>
@@ -1652,31 +1676,31 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>-1</v>
@@ -1715,7 +1739,7 @@
         <v>5</v>
       </c>
       <c r="AF11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG11">
         <v>5</v>
@@ -1724,10 +1748,10 @@
         <v>5</v>
       </c>
       <c r="AI11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK11">
         <v>-1</v>
@@ -1765,31 +1789,31 @@
         <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1822,16 +1846,16 @@
         <v>5</v>
       </c>
       <c r="AD12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF12">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH12">
         <v>5</v>
@@ -1840,7 +1864,7 @@
         <v>6</v>
       </c>
       <c r="AJ12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK12">
         <v>-1</v>
@@ -1878,31 +1902,31 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1935,25 +1959,25 @@
         <v>5</v>
       </c>
       <c r="AD13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG13">
         <v>5</v>
       </c>
       <c r="AH13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI13">
         <v>7</v>
       </c>
       <c r="AJ13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK13">
         <v>-1</v>
@@ -1991,31 +2015,31 @@
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -2045,25 +2069,25 @@
         <v>-1</v>
       </c>
       <c r="AC14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14">
         <v>5</v>
       </c>
       <c r="AH14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ14">
         <v>6</v>
@@ -2104,31 +2128,31 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -2164,22 +2188,22 @@
         <v>5</v>
       </c>
       <c r="AE15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK15">
         <v>-1</v>
@@ -2217,31 +2241,31 @@
         <v>5</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -2277,10 +2301,10 @@
         <v>5</v>
       </c>
       <c r="AE16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG16">
         <v>5</v>
@@ -2330,31 +2354,31 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -2387,10 +2411,10 @@
         <v>5</v>
       </c>
       <c r="AD17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF17">
         <v>9</v>
@@ -2399,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="AH17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI17">
         <v>5</v>
@@ -2443,31 +2467,31 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2503,7 +2527,7 @@
         <v>5</v>
       </c>
       <c r="AE18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF18">
         <v>5</v>
@@ -2512,7 +2536,7 @@
         <v>5</v>
       </c>
       <c r="AH18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI18">
         <v>5</v>
@@ -2556,31 +2580,31 @@
         <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2613,22 +2637,22 @@
         <v>6</v>
       </c>
       <c r="AD19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AI19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AJ19">
         <v>8</v>
@@ -2669,31 +2693,31 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2726,22 +2750,22 @@
         <v>6</v>
       </c>
       <c r="AD20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE20">
         <v>5</v>
       </c>
       <c r="AF20">
+        <v>8</v>
+      </c>
+      <c r="AG20">
+        <v>5</v>
+      </c>
+      <c r="AH20">
+        <v>8</v>
+      </c>
+      <c r="AI20">
         <v>9</v>
-      </c>
-      <c r="AG20">
-        <v>5</v>
-      </c>
-      <c r="AH20">
-        <v>6</v>
-      </c>
-      <c r="AI20">
-        <v>8</v>
       </c>
       <c r="AJ20">
         <v>7</v>
@@ -2782,31 +2806,31 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2836,13 +2860,13 @@
         <v>-1</v>
       </c>
       <c r="AC21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AE21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF21">
         <v>8</v>
@@ -2851,13 +2875,13 @@
         <v>5</v>
       </c>
       <c r="AH21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK21">
         <v>-1</v>
@@ -2895,31 +2919,31 @@
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2958,16 +2982,16 @@
         <v>5</v>
       </c>
       <c r="AF22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>5</v>
       </c>
       <c r="AH22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ22">
         <v>5</v>
@@ -3008,31 +3032,31 @@
         <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -3065,22 +3089,22 @@
         <v>5</v>
       </c>
       <c r="AD23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG23">
         <v>5</v>
       </c>
       <c r="AH23">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ23">
         <v>10</v>
@@ -3121,31 +3145,31 @@
         <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>-1</v>
@@ -3184,7 +3208,7 @@
         <v>5</v>
       </c>
       <c r="AF24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG24">
         <v>5</v>
@@ -3234,31 +3258,31 @@
         <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>-1</v>
@@ -3291,7 +3315,7 @@
         <v>6</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25">
         <v>9</v>
@@ -3347,31 +3371,31 @@
         <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>-1</v>
@@ -3407,10 +3431,10 @@
         <v>5</v>
       </c>
       <c r="AE26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG26">
         <v>5</v>
@@ -3419,10 +3443,10 @@
         <v>5</v>
       </c>
       <c r="AI26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK26">
         <v>-1</v>
@@ -3460,31 +3484,31 @@
         <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>-1</v>
@@ -3520,19 +3544,19 @@
         <v>7</v>
       </c>
       <c r="AE27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH27">
         <v>7</v>
       </c>
       <c r="AI27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ27">
         <v>8</v>
@@ -3573,31 +3597,31 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>-1</v>
@@ -3633,19 +3657,19 @@
         <v>5</v>
       </c>
       <c r="AE28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG28">
         <v>5</v>
       </c>
       <c r="AH28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ28">
         <v>5</v>
@@ -3686,31 +3710,31 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>-1</v>
@@ -3743,25 +3767,25 @@
         <v>6</v>
       </c>
       <c r="AD29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29">
         <v>8</v>
       </c>
       <c r="AF29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI29">
         <v>9</v>
       </c>
       <c r="AJ29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK29">
         <v>-1</v>
@@ -3799,31 +3823,31 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>-1</v>
@@ -3853,7 +3877,7 @@
         <v>-1</v>
       </c>
       <c r="AC30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD30">
         <v>5</v>
@@ -3862,19 +3886,19 @@
         <v>5</v>
       </c>
       <c r="AF30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG30">
         <v>5</v>
       </c>
       <c r="AH30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AK30">
         <v>-1</v>
@@ -3912,31 +3936,31 @@
         <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>-1</v>
@@ -3969,10 +3993,10 @@
         <v>5</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF31">
         <v>8</v>
@@ -3984,10 +4008,10 @@
         <v>5</v>
       </c>
       <c r="AI31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK31">
         <v>-1</v>
@@ -4025,31 +4049,31 @@
         <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>-1</v>
@@ -4082,16 +4106,16 @@
         <v>5</v>
       </c>
       <c r="AD32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF32">
         <v>9</v>
       </c>
       <c r="AG32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH32">
         <v>9</v>
@@ -4100,7 +4124,7 @@
         <v>10</v>
       </c>
       <c r="AJ32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK32">
         <v>-1</v>
@@ -4138,31 +4162,31 @@
         <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>-1</v>
@@ -4198,7 +4222,7 @@
         <v>5</v>
       </c>
       <c r="AE33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF33">
         <v>5</v>
@@ -4397,7 +4421,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -4406,16 +4430,16 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O4">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q4">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -4424,7 +4448,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -4433,16 +4457,16 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X4">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y4">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Z4">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -4483,25 +4507,25 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="L5">
+        <v>92.5</v>
+      </c>
+      <c r="M5">
+        <v>100</v>
+      </c>
+      <c r="N5">
         <v>95</v>
       </c>
-      <c r="M5">
-        <v>100</v>
-      </c>
-      <c r="N5">
-        <v>100</v>
-      </c>
       <c r="O5">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P5">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q5">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -4510,25 +4534,25 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="U5">
+        <v>92.5</v>
+      </c>
+      <c r="V5">
+        <v>100</v>
+      </c>
+      <c r="W5">
         <v>95</v>
       </c>
-      <c r="V5">
-        <v>100</v>
-      </c>
-      <c r="W5">
-        <v>100</v>
-      </c>
       <c r="X5">
-        <v>81.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y5">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z5">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AA5">
         <v>100</v>
@@ -4655,25 +4679,25 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="M7">
         <v>100</v>
       </c>
       <c r="N7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O7">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P7">
         <v>93.8</v>
       </c>
       <c r="Q7">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4682,25 +4706,25 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U7">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="V7">
         <v>100</v>
       </c>
       <c r="W7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X7">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y7">
         <v>93.8</v>
       </c>
       <c r="Z7">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AA7">
         <v>100</v>
@@ -4741,10 +4765,10 @@
         <v>100</v>
       </c>
       <c r="K8">
+        <v>18.2</v>
+      </c>
+      <c r="L8">
         <v>40</v>
-      </c>
-      <c r="L8">
-        <v>80</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -4753,25 +4777,25 @@
         <v>0</v>
       </c>
       <c r="O8">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="P8">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="Q8">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="R8">
-        <v>80</v>
+        <v>44.6</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T8">
+        <v>18.2</v>
+      </c>
+      <c r="U8">
         <v>40</v>
-      </c>
-      <c r="U8">
-        <v>80</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4780,19 +4804,19 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="Y8">
-        <v>62.5</v>
+        <v>31.3</v>
       </c>
       <c r="Z8">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>44.6</v>
       </c>
       <c r="AB8">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -4827,25 +4851,25 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M9">
         <v>100</v>
       </c>
       <c r="N9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O9">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="P9">
         <v>93.8</v>
       </c>
       <c r="Q9">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4854,25 +4878,25 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U9">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="V9">
         <v>100</v>
       </c>
       <c r="W9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X9">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="Y9">
         <v>93.8</v>
       </c>
       <c r="Z9">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="AA9">
         <v>100</v>
@@ -4913,7 +4937,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -4922,13 +4946,13 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O10">
         <v>100</v>
       </c>
       <c r="P10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -4940,7 +4964,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -4949,13 +4973,13 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X10">
         <v>100</v>
       </c>
       <c r="Y10">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z10">
         <v>100</v>
@@ -4999,58 +5023,58 @@
         <v>100</v>
       </c>
       <c r="K11">
+        <v>50</v>
+      </c>
+      <c r="L11">
+        <v>50</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>75</v>
+      </c>
+      <c r="O11">
+        <v>62.5</v>
+      </c>
+      <c r="P11">
+        <v>53.1</v>
+      </c>
+      <c r="Q11">
+        <v>80.5</v>
+      </c>
+      <c r="R11">
+        <v>53.7</v>
+      </c>
+      <c r="S11">
         <v>70</v>
       </c>
-      <c r="L11">
-        <v>80</v>
-      </c>
-      <c r="M11">
-        <v>100</v>
-      </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>81.3</v>
-      </c>
-      <c r="P11">
-        <v>81.3</v>
-      </c>
-      <c r="Q11">
-        <v>95</v>
-      </c>
-      <c r="R11">
-        <v>100</v>
-      </c>
-      <c r="S11">
-        <v>100</v>
-      </c>
       <c r="T11">
+        <v>50</v>
+      </c>
+      <c r="U11">
+        <v>50</v>
+      </c>
+      <c r="V11">
+        <v>100</v>
+      </c>
+      <c r="W11">
+        <v>75</v>
+      </c>
+      <c r="X11">
+        <v>62.5</v>
+      </c>
+      <c r="Y11">
+        <v>53.1</v>
+      </c>
+      <c r="Z11">
+        <v>80.5</v>
+      </c>
+      <c r="AA11">
+        <v>53.7</v>
+      </c>
+      <c r="AB11">
         <v>70</v>
-      </c>
-      <c r="U11">
-        <v>80</v>
-      </c>
-      <c r="V11">
-        <v>100</v>
-      </c>
-      <c r="W11">
-        <v>100</v>
-      </c>
-      <c r="X11">
-        <v>81.3</v>
-      </c>
-      <c r="Y11">
-        <v>81.3</v>
-      </c>
-      <c r="Z11">
-        <v>95</v>
-      </c>
-      <c r="AA11">
-        <v>100</v>
-      </c>
-      <c r="AB11">
-        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -5085,25 +5109,25 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="L12">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="M12">
         <v>100</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="O12">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="P12">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q12">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -5112,25 +5136,25 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="U12">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="V12">
         <v>100</v>
       </c>
       <c r="W12">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="X12">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Y12">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Z12">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -5171,7 +5195,7 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="L13">
         <v>95</v>
@@ -5180,16 +5204,16 @@
         <v>100</v>
       </c>
       <c r="N13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O13">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="P13">
         <v>87.5</v>
       </c>
-      <c r="P13">
-        <v>75</v>
-      </c>
       <c r="Q13">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -5198,7 +5222,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="U13">
         <v>95</v>
@@ -5207,16 +5231,16 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X13">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="Y13">
         <v>87.5</v>
       </c>
-      <c r="Y13">
-        <v>75</v>
-      </c>
       <c r="Z13">
-        <v>90</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -5257,7 +5281,7 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="L14">
         <v>75</v>
@@ -5266,16 +5290,16 @@
         <v>100</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="O14">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="P14">
         <v>75</v>
       </c>
       <c r="Q14">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -5284,7 +5308,7 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="U14">
         <v>75</v>
@@ -5293,16 +5317,16 @@
         <v>100</v>
       </c>
       <c r="W14">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="X14">
-        <v>87.5</v>
+        <v>75</v>
       </c>
       <c r="Y14">
         <v>75</v>
       </c>
       <c r="Z14">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -5343,7 +5367,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>80</v>
+        <v>54.5</v>
       </c>
       <c r="L15">
         <v>90</v>
@@ -5352,16 +5376,16 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O15">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="Q15">
-        <v>85</v>
+        <v>92.7</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -5370,7 +5394,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>80</v>
+        <v>54.5</v>
       </c>
       <c r="U15">
         <v>90</v>
@@ -5379,16 +5403,16 @@
         <v>100</v>
       </c>
       <c r="W15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X15">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y15">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="Z15">
-        <v>85</v>
+        <v>92.7</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -5429,7 +5453,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="L16">
         <v>75</v>
@@ -5438,16 +5462,16 @@
         <v>100</v>
       </c>
       <c r="N16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O16">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P16">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q16">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -5456,7 +5480,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="U16">
         <v>75</v>
@@ -5465,16 +5489,16 @@
         <v>100</v>
       </c>
       <c r="W16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X16">
-        <v>75</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="Y16">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Z16">
-        <v>95</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AA16">
         <v>100</v>
@@ -5515,7 +5539,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="L17">
         <v>95</v>
@@ -5524,16 +5548,16 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O17">
         <v>87.5</v>
       </c>
       <c r="P17">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q17">
-        <v>85</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -5542,7 +5566,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>70</v>
+        <v>81.8</v>
       </c>
       <c r="U17">
         <v>95</v>
@@ -5551,16 +5575,16 @@
         <v>100</v>
       </c>
       <c r="W17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X17">
         <v>87.5</v>
       </c>
       <c r="Y17">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z17">
-        <v>85</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AA17">
         <v>100</v>
@@ -5601,7 +5625,7 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="L18">
         <v>85</v>
@@ -5610,25 +5634,25 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>3.3</v>
+        <v>18.3</v>
       </c>
       <c r="O18">
+        <v>81.3</v>
+      </c>
+      <c r="P18">
+        <v>81.3</v>
+      </c>
+      <c r="Q18">
+        <v>78</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
         <v>87.5</v>
       </c>
-      <c r="P18">
-        <v>75</v>
-      </c>
-      <c r="Q18">
-        <v>85</v>
-      </c>
-      <c r="R18">
-        <v>100</v>
-      </c>
-      <c r="S18">
-        <v>100</v>
-      </c>
       <c r="T18">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="U18">
         <v>85</v>
@@ -5637,22 +5661,22 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>3.3</v>
+        <v>18.3</v>
       </c>
       <c r="X18">
+        <v>81.3</v>
+      </c>
+      <c r="Y18">
+        <v>81.3</v>
+      </c>
+      <c r="Z18">
+        <v>78</v>
+      </c>
+      <c r="AA18">
+        <v>100</v>
+      </c>
+      <c r="AB18">
         <v>87.5</v>
-      </c>
-      <c r="Y18">
-        <v>75</v>
-      </c>
-      <c r="Z18">
-        <v>85</v>
-      </c>
-      <c r="AA18">
-        <v>100</v>
-      </c>
-      <c r="AB18">
-        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -5687,7 +5711,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -5696,16 +5720,16 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="O19">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P19">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q19">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -5714,7 +5738,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5723,16 +5747,16 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="X19">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Y19">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z19">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AA19">
         <v>100</v>
@@ -5773,52 +5797,52 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L20">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M20">
         <v>100</v>
       </c>
       <c r="N20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P20">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q20">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+      <c r="T20">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="U20">
         <v>90</v>
       </c>
-      <c r="R20">
-        <v>100</v>
-      </c>
-      <c r="S20">
-        <v>100</v>
-      </c>
-      <c r="T20">
-        <v>80</v>
-      </c>
-      <c r="U20">
-        <v>95</v>
-      </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Y20">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z20">
-        <v>90</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AA20">
         <v>100</v>
@@ -5859,25 +5883,25 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="L21">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O21">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="P21">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q21">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -5886,25 +5910,25 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="U21">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X21">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Y21">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z21">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="AA21">
         <v>100</v>
@@ -5945,58 +5969,58 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>80</v>
+        <v>63.6</v>
       </c>
       <c r="L22">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="O22">
-        <v>81.3</v>
+        <v>59.4</v>
       </c>
       <c r="P22">
-        <v>93.8</v>
+        <v>68.8</v>
       </c>
       <c r="Q22">
+        <v>68.3</v>
+      </c>
+      <c r="R22">
+        <v>57.9</v>
+      </c>
+      <c r="S22">
+        <v>75</v>
+      </c>
+      <c r="T22">
+        <v>63.6</v>
+      </c>
+      <c r="U22">
         <v>85</v>
       </c>
-      <c r="R22">
-        <v>100</v>
-      </c>
-      <c r="S22">
-        <v>100</v>
-      </c>
-      <c r="T22">
-        <v>80</v>
-      </c>
-      <c r="U22">
-        <v>95</v>
-      </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="X22">
-        <v>81.3</v>
+        <v>59.4</v>
       </c>
       <c r="Y22">
-        <v>93.8</v>
+        <v>68.8</v>
       </c>
       <c r="Z22">
-        <v>85</v>
+        <v>68.3</v>
       </c>
       <c r="AA22">
-        <v>100</v>
+        <v>57.9</v>
       </c>
       <c r="AB22">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:28">
@@ -6031,25 +6055,25 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M23">
         <v>100</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O23">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P23">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q23">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -6058,25 +6082,25 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="U23">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V23">
         <v>100</v>
       </c>
       <c r="W23">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X23">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Y23">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z23">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -6117,16 +6141,16 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>80</v>
+        <v>77.3</v>
       </c>
       <c r="L24">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="O24">
         <v>87.5</v>
@@ -6135,25 +6159,25 @@
         <v>93.8</v>
       </c>
       <c r="Q24">
+        <v>92.7</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+      <c r="T24">
+        <v>77.3</v>
+      </c>
+      <c r="U24">
         <v>90</v>
       </c>
-      <c r="R24">
-        <v>100</v>
-      </c>
-      <c r="S24">
-        <v>100</v>
-      </c>
-      <c r="T24">
-        <v>80</v>
-      </c>
-      <c r="U24">
-        <v>95</v>
-      </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="X24">
         <v>87.5</v>
@@ -6162,7 +6186,7 @@
         <v>93.8</v>
       </c>
       <c r="Z24">
-        <v>90</v>
+        <v>92.7</v>
       </c>
       <c r="AA24">
         <v>100</v>
@@ -6203,7 +6227,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -6212,13 +6236,13 @@
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -6230,7 +6254,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -6239,13 +6263,13 @@
         <v>100</v>
       </c>
       <c r="W25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="X25">
         <v>100</v>
       </c>
       <c r="Y25">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z25">
         <v>100</v>
@@ -6289,22 +6313,22 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L26">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="O26">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P26">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -6316,22 +6340,22 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U26">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="V26">
         <v>100</v>
       </c>
       <c r="W26">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="X26">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Y26">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Z26">
         <v>100</v>
@@ -6375,25 +6399,25 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="L27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M27">
         <v>100</v>
       </c>
       <c r="N27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="O27">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="P27">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q27">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -6402,25 +6426,25 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="U27">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="X27">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="Y27">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z27">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -6461,7 +6485,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="L28">
         <v>75</v>
@@ -6470,7 +6494,7 @@
         <v>100</v>
       </c>
       <c r="N28">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="O28">
         <v>75</v>
@@ -6479,16 +6503,16 @@
         <v>75</v>
       </c>
       <c r="Q28">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S28">
         <v>100</v>
       </c>
       <c r="T28">
-        <v>70</v>
+        <v>63.6</v>
       </c>
       <c r="U28">
         <v>75</v>
@@ -6497,7 +6521,7 @@
         <v>100</v>
       </c>
       <c r="W28">
-        <v>100</v>
+        <v>88.3</v>
       </c>
       <c r="X28">
         <v>75</v>
@@ -6506,10 +6530,10 @@
         <v>75</v>
       </c>
       <c r="Z28">
-        <v>85</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AA28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB28">
         <v>100</v>
@@ -6547,10 +6571,10 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -6559,13 +6583,13 @@
         <v>100</v>
       </c>
       <c r="O29">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="P29">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q29">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -6574,10 +6598,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U29">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6586,13 +6610,13 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Y29">
-        <v>100</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z29">
-        <v>95</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AA29">
         <v>100</v>
@@ -6633,58 +6657,58 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>70</v>
+        <v>59.1</v>
       </c>
       <c r="L30">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="M30">
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O30">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="P30">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Q30">
-        <v>85</v>
+        <v>70.7</v>
       </c>
       <c r="R30">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T30">
-        <v>70</v>
+        <v>59.1</v>
       </c>
       <c r="U30">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="V30">
         <v>100</v>
       </c>
       <c r="W30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="X30">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Y30">
-        <v>93.8</v>
+        <v>87.5</v>
       </c>
       <c r="Z30">
-        <v>85</v>
+        <v>70.7</v>
       </c>
       <c r="AA30">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AB30">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:28">
@@ -6719,52 +6743,52 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>70</v>
+        <v>59.1</v>
       </c>
       <c r="L31">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="M31">
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="O31">
-        <v>87.5</v>
+        <v>81.3</v>
       </c>
       <c r="P31">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="Q31">
+        <v>90.2</v>
+      </c>
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+      <c r="T31">
+        <v>59.1</v>
+      </c>
+      <c r="U31">
+        <v>85</v>
+      </c>
+      <c r="V31">
+        <v>100</v>
+      </c>
+      <c r="W31">
+        <v>91.7</v>
+      </c>
+      <c r="X31">
         <v>81.3</v>
       </c>
-      <c r="Q31">
-        <v>90</v>
-      </c>
-      <c r="R31">
-        <v>100</v>
-      </c>
-      <c r="S31">
-        <v>100</v>
-      </c>
-      <c r="T31">
-        <v>70</v>
-      </c>
-      <c r="U31">
-        <v>90</v>
-      </c>
-      <c r="V31">
-        <v>100</v>
-      </c>
-      <c r="W31">
-        <v>100</v>
-      </c>
-      <c r="X31">
-        <v>87.5</v>
-      </c>
       <c r="Y31">
-        <v>81.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z31">
-        <v>90</v>
+        <v>90.2</v>
       </c>
       <c r="AA31">
         <v>100</v>
@@ -6805,52 +6829,52 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M32">
         <v>100</v>
       </c>
       <c r="N32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O32">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="P32">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Q32">
+        <v>92.7</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+      <c r="T32">
+        <v>77.3</v>
+      </c>
+      <c r="U32">
+        <v>92.5</v>
+      </c>
+      <c r="V32">
+        <v>100</v>
+      </c>
+      <c r="W32">
         <v>95</v>
       </c>
-      <c r="R32">
-        <v>100</v>
-      </c>
-      <c r="S32">
-        <v>100</v>
-      </c>
-      <c r="T32">
-        <v>70</v>
-      </c>
-      <c r="U32">
-        <v>100</v>
-      </c>
-      <c r="V32">
-        <v>100</v>
-      </c>
-      <c r="W32">
-        <v>100</v>
-      </c>
       <c r="X32">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="Y32">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="Z32">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="AA32">
         <v>100</v>
@@ -6891,55 +6915,55 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>70</v>
+        <v>31.8</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>52.5</v>
       </c>
       <c r="M33">
         <v>100</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O33">
-        <v>75</v>
+        <v>59.4</v>
       </c>
       <c r="P33">
-        <v>62.5</v>
+        <v>56.3</v>
       </c>
       <c r="Q33">
-        <v>85</v>
+        <v>73.2</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
       </c>
       <c r="T33">
-        <v>70</v>
+        <v>31.8</v>
       </c>
       <c r="U33">
-        <v>100</v>
+        <v>52.5</v>
       </c>
       <c r="V33">
         <v>100</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="X33">
-        <v>75</v>
+        <v>59.4</v>
       </c>
       <c r="Y33">
-        <v>62.5</v>
+        <v>56.3</v>
       </c>
       <c r="Z33">
-        <v>85</v>
+        <v>73.2</v>
       </c>
       <c r="AA33">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="AB33">
         <v>100</v>
@@ -7037,19 +7061,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2">
-        <v>26.7</v>
+        <v>36.7</v>
       </c>
       <c r="G3" s="2">
-        <v>73.3</v>
+        <v>63.3</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7060,7 +7084,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -7069,19 +7093,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F4" s="2">
-        <v>33.3</v>
+        <v>43.3</v>
       </c>
       <c r="G4" s="2">
-        <v>66.7</v>
+        <v>56.7</v>
       </c>
       <c r="H4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7092,7 +7116,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -7101,19 +7125,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F5" s="2">
-        <v>50</v>
+        <v>56.7</v>
       </c>
       <c r="G5" s="2">
-        <v>50</v>
+        <v>43.3</v>
       </c>
       <c r="H5">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7124,7 +7148,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -7133,19 +7157,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="2">
-        <v>60</v>
+        <v>56.7</v>
       </c>
       <c r="G6" s="2">
-        <v>40</v>
+        <v>43.3</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7156,7 +7180,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -7165,19 +7189,19 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2">
-        <v>60</v>
+        <v>76.7</v>
       </c>
       <c r="G7" s="2">
-        <v>40</v>
+        <v>23.3</v>
       </c>
       <c r="H7">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7197,19 +7221,19 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2">
-        <v>73.3</v>
+        <v>76.7</v>
       </c>
       <c r="G8" s="2">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="H8">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7220,7 +7244,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>64</v>
@@ -7229,19 +7253,19 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="G9" s="2">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="H9">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7261,19 +7285,19 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="2">
-        <v>90</v>
+        <v>86.7</v>
       </c>
       <c r="G10" s="2">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="H10">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7323,7 +7347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7355,22 +7379,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920180</v>
+        <v>23330051920185</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7378,16 +7402,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920180</v>
+        <v>23330051920185</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -7401,22 +7425,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920199</v>
+        <v>23330051920192</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7424,16 +7448,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920199</v>
+        <v>23330051920192</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -7447,22 +7471,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920210</v>
+        <v>22330051920050</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7470,16 +7494,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920210</v>
+        <v>22330051920050</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -7499,10 +7523,10 @@
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -7516,16 +7540,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920182</v>
+        <v>23330051920180</v>
       </c>
       <c r="B9" t="s">
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -7539,16 +7563,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920204</v>
+        <v>23330051920182</v>
       </c>
       <c r="B10" t="s">
         <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>13</v>
@@ -7562,16 +7586,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920206</v>
+        <v>23330051920199</v>
       </c>
       <c r="B11" t="s">
         <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -7585,16 +7609,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920186</v>
+        <v>23330051920204</v>
       </c>
       <c r="B12" t="s">
         <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>13</v>
@@ -7603,6 +7627,75 @@
         <v>57</v>
       </c>
       <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920206</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>57</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920186</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>23330051920210</v>
+      </c>
+      <c r="B15" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" t="s">
+        <v>100</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2AEV - Estadisticos 20232.xlsx
+++ b/grupos/2AEV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="124">
   <si>
     <t>Materia</t>
   </si>
@@ -194,18 +194,21 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Flores Paz Victor</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
+    <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Sanchez Hernández Raymundo</t>
   </si>
   <si>
@@ -215,9 +218,6 @@
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -230,28 +230,52 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BUSTOS</t>
+  </si>
+  <si>
+    <t>CERONIO</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
+    <t>FLORES</t>
   </si>
   <si>
     <t>LARA</t>
   </si>
   <si>
-    <t>PEREZ</t>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>NARVAEZ</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -263,22 +287,43 @@
     <t>TEQUIHUATLE</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>CRISTOBAL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>COCOTLE</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
+    <t>LAGUNA</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -287,28 +332,52 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>TRISTAN YABAL</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JOSE EMILIANO</t>
+  </si>
+  <si>
+    <t>JOSE ALDAIR</t>
+  </si>
+  <si>
+    <t>FERNANDO</t>
   </si>
   <si>
     <t>EMMANUEL</t>
   </si>
   <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
+    <t>JOSE ANTONIO</t>
   </si>
   <si>
     <t>DIEGO</t>
+  </si>
+  <si>
+    <t>JUAN RAMON</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
   </si>
   <si>
     <t>ROBBIE ALONSO</t>
@@ -912,34 +981,34 @@
         <v>10</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>10</v>
@@ -957,7 +1026,7 @@
         <v>9</v>
       </c>
       <c r="AI4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ4">
         <v>8</v>
@@ -1025,40 +1094,40 @@
         <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD5">
         <v>7</v>
       </c>
       <c r="AE5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF5">
         <v>8</v>
@@ -1070,7 +1139,7 @@
         <v>10</v>
       </c>
       <c r="AI5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ5">
         <v>7</v>
@@ -1138,31 +1207,31 @@
         <v>10</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -1174,7 +1243,7 @@
         <v>10</v>
       </c>
       <c r="AF6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG6">
         <v>9</v>
@@ -1251,52 +1320,52 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE7">
         <v>7</v>
       </c>
       <c r="AF7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH7">
         <v>6</v>
       </c>
       <c r="AI7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7">
         <v>9</v>
@@ -1364,31 +1433,31 @@
         <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>5</v>
@@ -1477,37 +1546,37 @@
         <v>10</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC9">
         <v>6</v>
       </c>
       <c r="AD9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE9">
         <v>6</v>
@@ -1516,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="AG9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH9">
         <v>7</v>
@@ -1525,7 +1594,7 @@
         <v>8</v>
       </c>
       <c r="AJ9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK9">
         <v>-1</v>
@@ -1590,34 +1659,34 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD10">
         <v>9</v>
@@ -1703,31 +1772,31 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC11">
         <v>5</v>
@@ -1736,10 +1805,10 @@
         <v>5</v>
       </c>
       <c r="AE11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG11">
         <v>5</v>
@@ -1748,10 +1817,10 @@
         <v>5</v>
       </c>
       <c r="AI11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK11">
         <v>-1</v>
@@ -1816,31 +1885,31 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC12">
         <v>5</v>
@@ -1852,16 +1921,16 @@
         <v>6</v>
       </c>
       <c r="AF12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH12">
         <v>5</v>
       </c>
       <c r="AI12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ12">
         <v>7</v>
@@ -1929,31 +1998,31 @@
         <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC13">
         <v>5</v>
@@ -1968,7 +2037,7 @@
         <v>7</v>
       </c>
       <c r="AG13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH13">
         <v>6</v>
@@ -2042,49 +2111,49 @@
         <v>5</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
         <v>7</v>
       </c>
       <c r="AD14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE14">
         <v>6</v>
       </c>
       <c r="AF14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI14">
         <v>7</v>
@@ -2155,52 +2224,52 @@
         <v>10</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE15">
         <v>7</v>
       </c>
       <c r="AF15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>8</v>
       </c>
       <c r="AH15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ15">
         <v>7</v>
@@ -2268,31 +2337,31 @@
         <v>10</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>5</v>
@@ -2310,13 +2379,13 @@
         <v>5</v>
       </c>
       <c r="AH16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK16">
         <v>-1</v>
@@ -2381,31 +2450,31 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC17">
         <v>5</v>
@@ -2420,13 +2489,13 @@
         <v>9</v>
       </c>
       <c r="AG17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ17">
         <v>8</v>
@@ -2494,37 +2563,37 @@
         <v>5</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC18">
         <v>5</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE18">
         <v>6</v>
@@ -2533,16 +2602,16 @@
         <v>5</v>
       </c>
       <c r="AG18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH18">
         <v>6</v>
       </c>
       <c r="AI18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK18">
         <v>-1</v>
@@ -2607,43 +2676,43 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC19">
         <v>6</v>
       </c>
       <c r="AD19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE19">
         <v>7</v>
       </c>
       <c r="AF19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG19">
         <v>8</v>
@@ -2720,49 +2789,49 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD20">
         <v>8</v>
       </c>
       <c r="AE20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF20">
         <v>8</v>
       </c>
       <c r="AG20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI20">
         <v>9</v>
@@ -2833,37 +2902,37 @@
         <v>10</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE21">
         <v>6</v>
@@ -2872,16 +2941,16 @@
         <v>8</v>
       </c>
       <c r="AG21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK21">
         <v>-1</v>
@@ -2946,43 +3015,43 @@
         <v>5</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC22">
         <v>5</v>
       </c>
       <c r="AD22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG22">
         <v>5</v>
@@ -2991,7 +3060,7 @@
         <v>5</v>
       </c>
       <c r="AI22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ22">
         <v>5</v>
@@ -3059,37 +3128,37 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AE23">
         <v>6</v>
@@ -3098,13 +3167,13 @@
         <v>7</v>
       </c>
       <c r="AG23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH23">
         <v>5</v>
       </c>
       <c r="AI23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ23">
         <v>10</v>
@@ -3172,31 +3241,31 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC24">
         <v>5</v>
@@ -3205,13 +3274,13 @@
         <v>8</v>
       </c>
       <c r="AE24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH24">
         <v>6</v>
@@ -3285,40 +3354,40 @@
         <v>10</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC25">
         <v>6</v>
       </c>
       <c r="AD25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF25">
         <v>10</v>
@@ -3333,7 +3402,7 @@
         <v>8</v>
       </c>
       <c r="AJ25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK25">
         <v>-1</v>
@@ -3398,37 +3467,37 @@
         <v>10</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE26">
         <v>6</v>
@@ -3437,13 +3506,13 @@
         <v>7</v>
       </c>
       <c r="AG26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ26">
         <v>8</v>
@@ -3511,34 +3580,34 @@
         <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD27">
         <v>7</v>
@@ -3624,55 +3693,55 @@
         <v>10</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC28">
         <v>5</v>
       </c>
       <c r="AD28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE28">
         <v>6</v>
       </c>
       <c r="AF28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28">
         <v>5</v>
       </c>
       <c r="AH28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK28">
         <v>-1</v>
@@ -3737,40 +3806,40 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD29">
         <v>9</v>
       </c>
       <c r="AE29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF29">
         <v>9</v>
@@ -3779,7 +3848,7 @@
         <v>7</v>
       </c>
       <c r="AH29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI29">
         <v>9</v>
@@ -3850,31 +3919,31 @@
         <v>5</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC30">
         <v>5</v>
@@ -3883,10 +3952,10 @@
         <v>5</v>
       </c>
       <c r="AE30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG30">
         <v>5</v>
@@ -3895,7 +3964,7 @@
         <v>5</v>
       </c>
       <c r="AI30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AJ30">
         <v>5</v>
@@ -3963,31 +4032,31 @@
         <v>10</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC31">
         <v>5</v>
@@ -4002,16 +4071,16 @@
         <v>8</v>
       </c>
       <c r="AG31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK31">
         <v>-1</v>
@@ -4076,31 +4145,31 @@
         <v>10</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC32">
         <v>5</v>
@@ -4115,13 +4184,13 @@
         <v>9</v>
       </c>
       <c r="AG32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ32">
         <v>9</v>
@@ -4189,31 +4258,31 @@
         <v>10</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC33">
         <v>5</v>
@@ -4448,7 +4517,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>86.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="U4">
         <v>100</v>
@@ -4457,16 +4526,16 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="X4">
-        <v>90.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y4">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="Z4">
-        <v>92.7</v>
+        <v>93.5</v>
       </c>
       <c r="AA4">
         <v>100</v>
@@ -4534,25 +4603,25 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>77.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U5">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="V5">
         <v>100</v>
       </c>
       <c r="W5">
-        <v>95</v>
+        <v>86.5</v>
       </c>
       <c r="X5">
-        <v>90.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="Y5">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z5">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AA5">
         <v>100</v>
@@ -4632,7 +4701,7 @@
         <v>100</v>
       </c>
       <c r="X6">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Y6">
         <v>100</v>
@@ -4706,25 +4775,25 @@
         <v>100</v>
       </c>
       <c r="T7">
-        <v>86.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="U7">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="V7">
         <v>100</v>
       </c>
       <c r="W7">
-        <v>96.7</v>
+        <v>94.8</v>
       </c>
       <c r="X7">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y7">
         <v>93.8</v>
       </c>
       <c r="Z7">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AA7">
         <v>100</v>
@@ -4792,10 +4861,10 @@
         <v>50</v>
       </c>
       <c r="T8">
-        <v>18.2</v>
+        <v>12.9</v>
       </c>
       <c r="U8">
-        <v>40</v>
+        <v>26.7</v>
       </c>
       <c r="V8">
         <v>100</v>
@@ -4804,19 +4873,19 @@
         <v>0</v>
       </c>
       <c r="X8">
-        <v>37.5</v>
+        <v>25</v>
       </c>
       <c r="Y8">
-        <v>31.3</v>
+        <v>20.8</v>
       </c>
       <c r="Z8">
-        <v>39</v>
+        <v>25.8</v>
       </c>
       <c r="AA8">
-        <v>44.6</v>
+        <v>31.8</v>
       </c>
       <c r="AB8">
-        <v>50</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="9" spans="1:28">
@@ -4878,25 +4947,25 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>90.90000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U9">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="V9">
         <v>100</v>
       </c>
       <c r="W9">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="X9">
-        <v>81.3</v>
+        <v>91.7</v>
       </c>
       <c r="Y9">
-        <v>93.8</v>
+        <v>91.7</v>
       </c>
       <c r="Z9">
-        <v>92.7</v>
+        <v>93.5</v>
       </c>
       <c r="AA9">
         <v>100</v>
@@ -4964,7 +5033,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>81.8</v>
+        <v>90.3</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -4973,16 +5042,16 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X10">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y10">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="Z10">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA10">
         <v>100</v>
@@ -5050,31 +5119,31 @@
         <v>70</v>
       </c>
       <c r="T11">
-        <v>50</v>
+        <v>35.5</v>
       </c>
       <c r="U11">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="V11">
         <v>100</v>
       </c>
       <c r="W11">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="X11">
-        <v>62.5</v>
+        <v>41.7</v>
       </c>
       <c r="Y11">
-        <v>53.1</v>
+        <v>35.4</v>
       </c>
       <c r="Z11">
-        <v>80.5</v>
+        <v>61.3</v>
       </c>
       <c r="AA11">
-        <v>53.7</v>
+        <v>38.1</v>
       </c>
       <c r="AB11">
-        <v>70</v>
+        <v>58.3</v>
       </c>
     </row>
     <row r="12" spans="1:28">
@@ -5136,25 +5205,25 @@
         <v>100</v>
       </c>
       <c r="T12">
-        <v>77.3</v>
+        <v>67.7</v>
       </c>
       <c r="U12">
+        <v>90</v>
+      </c>
+      <c r="V12">
+        <v>100</v>
+      </c>
+      <c r="W12">
         <v>87.5</v>
       </c>
-      <c r="V12">
-        <v>100</v>
-      </c>
-      <c r="W12">
-        <v>85</v>
-      </c>
       <c r="X12">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Y12">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="Z12">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AA12">
         <v>100</v>
@@ -5222,7 +5291,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>77.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="U13">
         <v>95</v>
@@ -5231,16 +5300,16 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X13">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y13">
         <v>87.5</v>
       </c>
       <c r="Z13">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AA13">
         <v>100</v>
@@ -5308,31 +5377,31 @@
         <v>0</v>
       </c>
       <c r="T14">
-        <v>81.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U14">
-        <v>75</v>
+        <v>81.7</v>
       </c>
       <c r="V14">
         <v>100</v>
       </c>
       <c r="W14">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X14">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="Y14">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="Z14">
-        <v>78</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AA14">
         <v>100</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="15" spans="1:28">
@@ -5394,25 +5463,25 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>54.5</v>
+        <v>71</v>
       </c>
       <c r="U15">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="V15">
         <v>100</v>
       </c>
       <c r="W15">
-        <v>96.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="X15">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y15">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="Z15">
-        <v>92.7</v>
+        <v>95.2</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -5480,7 +5549,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>63.6</v>
+        <v>51.6</v>
       </c>
       <c r="U16">
         <v>75</v>
@@ -5489,16 +5558,16 @@
         <v>100</v>
       </c>
       <c r="W16">
-        <v>96.7</v>
+        <v>88.5</v>
       </c>
       <c r="X16">
-        <v>78.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Y16">
-        <v>81.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z16">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="AA16">
         <v>100</v>
@@ -5566,25 +5635,25 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>81.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="U17">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="V17">
         <v>100</v>
       </c>
       <c r="W17">
-        <v>96.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X17">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="Y17">
-        <v>84.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z17">
-        <v>85.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="AA17">
         <v>100</v>
@@ -5652,31 +5721,31 @@
         <v>87.5</v>
       </c>
       <c r="T18">
-        <v>63.6</v>
+        <v>67.7</v>
       </c>
       <c r="U18">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V18">
         <v>100</v>
       </c>
       <c r="W18">
-        <v>18.3</v>
+        <v>33.3</v>
       </c>
       <c r="X18">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Y18">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Z18">
-        <v>78</v>
+        <v>85.5</v>
       </c>
       <c r="AA18">
         <v>100</v>
       </c>
       <c r="AB18">
-        <v>87.5</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:28">
@@ -5738,7 +5807,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>86.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5747,16 +5816,16 @@
         <v>100</v>
       </c>
       <c r="W19">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="X19">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Y19">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z19">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AA19">
         <v>100</v>
@@ -5824,25 +5893,25 @@
         <v>100</v>
       </c>
       <c r="T20">
-        <v>86.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="U20">
-        <v>90</v>
+        <v>93.3</v>
       </c>
       <c r="V20">
         <v>100</v>
       </c>
       <c r="W20">
-        <v>96.7</v>
+        <v>94.8</v>
       </c>
       <c r="X20">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="Y20">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z20">
-        <v>85.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="AA20">
         <v>100</v>
@@ -5910,25 +5979,25 @@
         <v>100</v>
       </c>
       <c r="T21">
-        <v>77.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U21">
-        <v>87.5</v>
+        <v>90</v>
       </c>
       <c r="V21">
         <v>100</v>
       </c>
       <c r="W21">
-        <v>93.3</v>
+        <v>92.7</v>
       </c>
       <c r="X21">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="Y21">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z21">
-        <v>90.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AA21">
         <v>100</v>
@@ -5996,31 +6065,31 @@
         <v>75</v>
       </c>
       <c r="T22">
-        <v>63.6</v>
+        <v>45.2</v>
       </c>
       <c r="U22">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="V22">
         <v>100</v>
       </c>
       <c r="W22">
-        <v>88.3</v>
+        <v>55.2</v>
       </c>
       <c r="X22">
-        <v>59.4</v>
+        <v>39.6</v>
       </c>
       <c r="Y22">
-        <v>68.8</v>
+        <v>45.8</v>
       </c>
       <c r="Z22">
-        <v>68.3</v>
+        <v>45.2</v>
       </c>
       <c r="AA22">
-        <v>57.9</v>
+        <v>40.9</v>
       </c>
       <c r="AB22">
-        <v>75</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="23" spans="1:28">
@@ -6082,25 +6151,25 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>81.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U23">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="V23">
         <v>100</v>
       </c>
       <c r="W23">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="X23">
-        <v>84.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y23">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z23">
-        <v>90.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AA23">
         <v>100</v>
@@ -6168,25 +6237,25 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>77.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="U24">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="V24">
         <v>100</v>
       </c>
       <c r="W24">
-        <v>93.3</v>
+        <v>94.8</v>
       </c>
       <c r="X24">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="Y24">
-        <v>93.8</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z24">
-        <v>92.7</v>
+        <v>93.5</v>
       </c>
       <c r="AA24">
         <v>100</v>
@@ -6254,7 +6323,7 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>81.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U25">
         <v>100</v>
@@ -6263,13 +6332,13 @@
         <v>100</v>
       </c>
       <c r="W25">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X25">
         <v>100</v>
       </c>
       <c r="Y25">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="Z25">
         <v>100</v>
@@ -6340,22 +6409,22 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>86.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="U26">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="V26">
         <v>100</v>
       </c>
       <c r="W26">
+        <v>87.5</v>
+      </c>
+      <c r="X26">
+        <v>95.8</v>
+      </c>
+      <c r="Y26">
         <v>91.7</v>
-      </c>
-      <c r="X26">
-        <v>93.8</v>
-      </c>
-      <c r="Y26">
-        <v>93.8</v>
       </c>
       <c r="Z26">
         <v>100</v>
@@ -6426,25 +6495,25 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>81.8</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="U27">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="V27">
         <v>100</v>
       </c>
       <c r="W27">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="X27">
         <v>93.8</v>
       </c>
       <c r="Y27">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Z27">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -6512,28 +6581,28 @@
         <v>100</v>
       </c>
       <c r="T28">
-        <v>63.6</v>
+        <v>51.6</v>
       </c>
       <c r="U28">
-        <v>75</v>
+        <v>81.7</v>
       </c>
       <c r="V28">
         <v>100</v>
       </c>
       <c r="W28">
-        <v>88.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X28">
-        <v>75</v>
+        <v>68.8</v>
       </c>
       <c r="Y28">
-        <v>75</v>
+        <v>83.3</v>
       </c>
       <c r="Z28">
-        <v>82.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="AA28">
-        <v>95</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AB28">
         <v>100</v>
@@ -6598,10 +6667,10 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>86.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="U29">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="V29">
         <v>100</v>
@@ -6610,13 +6679,13 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y29">
-        <v>90.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="Z29">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AA29">
         <v>100</v>
@@ -6684,31 +6753,31 @@
         <v>50</v>
       </c>
       <c r="T30">
-        <v>59.1</v>
+        <v>41.9</v>
       </c>
       <c r="U30">
-        <v>55</v>
+        <v>68.3</v>
       </c>
       <c r="V30">
         <v>100</v>
       </c>
       <c r="W30">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="X30">
-        <v>71.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="Y30">
-        <v>87.5</v>
+        <v>58.3</v>
       </c>
       <c r="Z30">
-        <v>70.7</v>
+        <v>46.8</v>
       </c>
       <c r="AA30">
-        <v>90.90000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="AB30">
-        <v>50</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="31" spans="1:28">
@@ -6770,25 +6839,25 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>59.1</v>
+        <v>61.3</v>
       </c>
       <c r="U31">
-        <v>85</v>
+        <v>88.3</v>
       </c>
       <c r="V31">
         <v>100</v>
       </c>
       <c r="W31">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="X31">
-        <v>81.3</v>
+        <v>87.5</v>
       </c>
       <c r="Y31">
-        <v>84.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z31">
-        <v>90.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AA31">
         <v>100</v>
@@ -6856,25 +6925,25 @@
         <v>100</v>
       </c>
       <c r="T32">
-        <v>77.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="U32">
-        <v>92.5</v>
+        <v>93.3</v>
       </c>
       <c r="V32">
         <v>100</v>
       </c>
       <c r="W32">
-        <v>95</v>
+        <v>92.7</v>
       </c>
       <c r="X32">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="Y32">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="Z32">
-        <v>92.7</v>
+        <v>93.5</v>
       </c>
       <c r="AA32">
         <v>100</v>
@@ -6942,28 +7011,28 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>31.8</v>
+        <v>22.6</v>
       </c>
       <c r="U33">
-        <v>52.5</v>
+        <v>35</v>
       </c>
       <c r="V33">
         <v>100</v>
       </c>
       <c r="W33">
-        <v>45</v>
+        <v>28.1</v>
       </c>
       <c r="X33">
-        <v>59.4</v>
+        <v>39.6</v>
       </c>
       <c r="Y33">
         <v>56.3</v>
       </c>
       <c r="Z33">
-        <v>73.2</v>
+        <v>62.9</v>
       </c>
       <c r="AA33">
-        <v>90.90000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="AB33">
         <v>100</v>
@@ -7052,7 +7121,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -7061,19 +7130,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F3" s="2">
-        <v>36.7</v>
+        <v>46.7</v>
       </c>
       <c r="G3" s="2">
-        <v>63.3</v>
+        <v>53.3</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7084,7 +7153,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -7093,19 +7162,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>43.3</v>
+        <v>76.7</v>
       </c>
       <c r="G4" s="2">
-        <v>56.7</v>
+        <v>23.3</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7116,7 +7185,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -7125,16 +7194,16 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>56.7</v>
+        <v>76.7</v>
       </c>
       <c r="G5" s="2">
-        <v>43.3</v>
+        <v>23.3</v>
       </c>
       <c r="H5">
         <v>6.6</v>
@@ -7157,19 +7226,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>56.7</v>
+        <v>76.7</v>
       </c>
       <c r="G6" s="2">
-        <v>43.3</v>
+        <v>23.3</v>
       </c>
       <c r="H6">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7180,7 +7249,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -7189,16 +7258,16 @@
         <v>30</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="G7" s="2">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -7212,7 +7281,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>63</v>
@@ -7221,16 +7290,16 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2">
-        <v>76.7</v>
+        <v>83.3</v>
       </c>
       <c r="G8" s="2">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -7244,7 +7313,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>64</v>
@@ -7253,19 +7322,19 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="G9" s="2">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -7276,7 +7345,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>65</v>
@@ -7285,19 +7354,19 @@
         <v>30</v>
       </c>
       <c r="D10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>86.7</v>
+        <v>96.7</v>
       </c>
       <c r="G10" s="2">
-        <v>13.3</v>
+        <v>3.3</v>
       </c>
       <c r="H10">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -7347,7 +7416,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7379,19 +7448,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920185</v>
+        <v>23330051920192</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
         <v>58</v>
@@ -7402,16 +7471,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920185</v>
+        <v>23330051920192</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
         <v>13</v>
@@ -7425,22 +7494,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920192</v>
+        <v>23330051920329</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7448,16 +7517,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920192</v>
+        <v>23330051920329</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
         <v>13</v>
@@ -7471,22 +7540,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920050</v>
+        <v>22330051920196</v>
       </c>
       <c r="B6" t="s">
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7494,16 +7563,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920050</v>
+        <v>22330051920196</v>
       </c>
       <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
         <v>13</v>
@@ -7517,39 +7586,39 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920179</v>
+        <v>23330051920203</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920180</v>
+        <v>23330051920203</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>13</v>
@@ -7563,39 +7632,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920182</v>
+        <v>23330051920332</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920199</v>
+        <v>23330051920332</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -7609,39 +7678,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920204</v>
+        <v>23330051920211</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920206</v>
+        <v>23330051920211</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>13</v>
@@ -7655,39 +7724,39 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920186</v>
+        <v>22330051920050</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920210</v>
+        <v>22330051920050</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
@@ -7696,6 +7765,305 @@
         <v>57</v>
       </c>
       <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>23330051920179</v>
+      </c>
+      <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>57</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920180</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>57</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920182</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920183</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920185</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920389</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920199</v>
+      </c>
+      <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" t="s">
+        <v>57</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920201</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920202</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" t="s">
+        <v>13</v>
+      </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920204</v>
+      </c>
+      <c r="B25" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+      <c r="D25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920206</v>
+      </c>
+      <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920186</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
+        <v>122</v>
+      </c>
+      <c r="E27" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920210</v>
+      </c>
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2AEV - Estadisticos 20232.xlsx
+++ b/grupos/2AEV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="101">
   <si>
     <t>Materia</t>
   </si>
@@ -191,24 +191,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
+    <t>Flores Paz Victor</t>
+  </si>
+  <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
-    <t>Flores Paz Victor</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
-  </si>
-  <si>
     <t>Sanchez Hernández Raymundo</t>
   </si>
   <si>
@@ -230,6 +230,12 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -251,40 +257,16 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BUSTOS</t>
-  </si>
-  <si>
-    <t>CERONIO</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
   </si>
   <si>
     <t>CARRERA</t>
@@ -308,28 +290,16 @@
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
-  </si>
-  <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>SERGIO EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
   </si>
   <si>
     <t>KEVYN DANIEL</t>
@@ -351,45 +321,6 @@
   </si>
   <si>
     <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JOSE EMILIANO</t>
-  </si>
-  <si>
-    <t>JOSE ALDAIR</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JUAN RAMON</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>ROBBIE ALONSO</t>
-  </si>
-  <si>
-    <t>ANTHONY</t>
-  </si>
-  <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
-    <t>ISAAC</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +963,7 @@
         <v>8</v>
       </c>
       <c r="AK4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1145,7 +1076,7 @@
         <v>7</v>
       </c>
       <c r="AK5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1258,7 +1189,7 @@
         <v>9</v>
       </c>
       <c r="AK6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1371,7 +1302,7 @@
         <v>9</v>
       </c>
       <c r="AK7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1484,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="AK8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1597,7 +1528,7 @@
         <v>7</v>
       </c>
       <c r="AK9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1710,7 +1641,7 @@
         <v>9</v>
       </c>
       <c r="AK10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1823,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="AK11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1936,7 +1867,7 @@
         <v>7</v>
       </c>
       <c r="AK12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2049,7 +1980,7 @@
         <v>7</v>
       </c>
       <c r="AK13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2162,7 +2093,7 @@
         <v>6</v>
       </c>
       <c r="AK14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2275,7 +2206,7 @@
         <v>7</v>
       </c>
       <c r="AK15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2388,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="AK16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2501,7 +2432,7 @@
         <v>8</v>
       </c>
       <c r="AK17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -2614,7 +2545,7 @@
         <v>6</v>
       </c>
       <c r="AK18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -2727,7 +2658,7 @@
         <v>8</v>
       </c>
       <c r="AK19">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -2840,7 +2771,7 @@
         <v>7</v>
       </c>
       <c r="AK20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -2953,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="AK21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3066,7 +2997,7 @@
         <v>5</v>
       </c>
       <c r="AK22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3179,7 +3110,7 @@
         <v>10</v>
       </c>
       <c r="AK23">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3292,7 +3223,7 @@
         <v>7</v>
       </c>
       <c r="AK24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3405,7 +3336,7 @@
         <v>8</v>
       </c>
       <c r="AK25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3518,7 +3449,7 @@
         <v>8</v>
       </c>
       <c r="AK26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -3631,7 +3562,7 @@
         <v>8</v>
       </c>
       <c r="AK27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -3744,7 +3675,7 @@
         <v>6</v>
       </c>
       <c r="AK28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -3857,7 +3788,7 @@
         <v>9</v>
       </c>
       <c r="AK29">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -3970,7 +3901,7 @@
         <v>5</v>
       </c>
       <c r="AK30">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4083,7 +4014,7 @@
         <v>8</v>
       </c>
       <c r="AK31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4196,7 +4127,7 @@
         <v>9</v>
       </c>
       <c r="AK32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4309,7 +4240,7 @@
         <v>5</v>
       </c>
       <c r="AK33">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -7092,7 +7023,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
@@ -7101,27 +7032,30 @@
         <v>30</v>
       </c>
       <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46.7</v>
+      </c>
+      <c r="G2" s="2">
+        <v>53.3</v>
+      </c>
+      <c r="H2">
+        <v>5.7</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>30</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
@@ -7130,19 +7064,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>46.7</v>
+        <v>76.7</v>
       </c>
       <c r="G3" s="2">
-        <v>53.3</v>
+        <v>23.3</v>
       </c>
       <c r="H3">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7153,7 +7087,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>59</v>
@@ -7174,7 +7108,7 @@
         <v>23.3</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7185,7 +7119,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>60</v>
@@ -7206,7 +7140,7 @@
         <v>23.3</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7217,7 +7151,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>61</v>
@@ -7226,19 +7160,19 @@
         <v>30</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>76.7</v>
+        <v>80</v>
       </c>
       <c r="G6" s="2">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7249,7 +7183,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>62</v>
@@ -7270,7 +7204,7 @@
         <v>20</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7416,7 +7350,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7448,22 +7382,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920192</v>
+        <v>23330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7471,45 +7405,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920192</v>
+        <v>23330051920190</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920329</v>
+        <v>23330051920189</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7517,45 +7451,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920329</v>
+        <v>23330051920189</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920196</v>
+        <v>23330051920208</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7563,45 +7497,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920196</v>
+        <v>23330051920208</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920203</v>
+        <v>22330051920389</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7609,45 +7543,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920203</v>
+        <v>23330051920192</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>57</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920332</v>
+        <v>23330051920329</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7655,45 +7589,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920332</v>
+        <v>22330051920196</v>
       </c>
       <c r="B11" t="s">
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920211</v>
+        <v>23330051920203</v>
       </c>
       <c r="B12" t="s">
         <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7701,45 +7635,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920211</v>
+        <v>23330051920332</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>57</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920050</v>
+        <v>23330051920211</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7750,321 +7684,22 @@
         <v>22330051920050</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>57</v>
       </c>
       <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920179</v>
-      </c>
-      <c r="B16" t="s">
-        <v>77</v>
-      </c>
-      <c r="C16" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920180</v>
-      </c>
-      <c r="B17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C17" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920182</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920183</v>
-      </c>
-      <c r="B19" t="s">
-        <v>80</v>
-      </c>
-      <c r="C19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920185</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" t="s">
-        <v>115</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>57</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920389</v>
-      </c>
-      <c r="B21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
-      </c>
-      <c r="D21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920199</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="D22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920201</v>
-      </c>
-      <c r="B23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920202</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920204</v>
-      </c>
-      <c r="B25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>103</v>
-      </c>
-      <c r="D25" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920206</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920186</v>
-      </c>
-      <c r="B27" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" t="s">
-        <v>122</v>
-      </c>
-      <c r="E27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F27" t="s">
-        <v>57</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920210</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>88</v>
-      </c>
-      <c r="D28" t="s">
-        <v>123</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
